--- a/checklist_forms/044_vehicle_inspection_knowledge_quiz--checklist_forms.xlsx
+++ b/checklist_forms/044_vehicle_inspection_knowledge_quiz--checklist_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1098,7 +1098,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C36"/>
+  <dimension ref="A1:C34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="29" customWidth="1" min="1" max="1"/>
@@ -1449,7 +1449,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>correct_statement_choices</t>
+          <t>correct_statement_2_choices</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1471,12 +1471,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>a)_yes</t>
+          <t>b)_no</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>a) Yes</t>
+          <t>b) No</t>
         </is>
       </c>
     </row>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>b)_no</t>
+          <t>a)_no</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>b) No</t>
+          <t>a) No</t>
         </is>
       </c>
     </row>
@@ -1505,46 +1505,46 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>a)_no</t>
+          <t>b)_yes</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>a) No</t>
+          <t>b) Yes</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>correct_statement_2_choices</t>
+          <t>question_5_choices</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>b)_yes</t>
+          <t>option_a</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>b) Yes</t>
+          <t>Option A</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>correct_statement_2_choices</t>
+          <t>question_5_choices</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>a)_yes</t>
+          <t>option_b</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>a) Yes</t>
+          <t>Option B</t>
         </is>
       </c>
     </row>
@@ -1556,12 +1556,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>option_a</t>
+          <t>option_c</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Option A</t>
+          <t>Option C</t>
         </is>
       </c>
     </row>
@@ -1573,12 +1573,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>option_b</t>
+          <t>option_d</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Option B</t>
+          <t>Option D</t>
         </is>
       </c>
     </row>
@@ -1590,46 +1590,46 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>option_c</t>
+          <t>option_e</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Option C</t>
+          <t>Option E</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>question_5_choices</t>
+          <t>correct_answer_1_choices</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>option_d</t>
+          <t>a</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Option D</t>
+          <t>A</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>question_5_choices</t>
+          <t>correct_answer_1_choices</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>option_e</t>
+          <t>b</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Option E</t>
+          <t>B</t>
         </is>
       </c>
     </row>
@@ -1641,12 +1641,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>a</t>
+          <t>c</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
     </row>
@@ -1658,12 +1658,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>b</t>
+          <t>d</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>D</t>
         </is>
       </c>
     </row>
@@ -1675,44 +1675,10 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>c</t>
+          <t>e</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>correct_answer_1_choices</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>d</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>correct_answer_1_choices</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>e</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
         <is>
           <t>E</t>
         </is>
